--- a/results/data/semih_async_dqn_experiment_results.xlsx
+++ b/results/data/semih_async_dqn_experiment_results.xlsx
@@ -750,190 +750,190 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>143.3</v>
+        <v>164.7</v>
       </c>
       <c r="C2" t="n">
-        <v>7.963039620647383</v>
+        <v>6.634003316248795</v>
       </c>
       <c r="D2" t="n">
-        <v>141.1</v>
+        <v>162.6</v>
       </c>
       <c r="E2" t="n">
-        <v>4.036087214122113</v>
+        <v>3.292415526630866</v>
       </c>
       <c r="F2" t="n">
-        <v>143.9</v>
+        <v>165.7</v>
       </c>
       <c r="G2" t="n">
-        <v>9.004998611882181</v>
+        <v>4.775981574503821</v>
       </c>
       <c r="H2" t="n">
-        <v>141.3</v>
+        <v>159.4</v>
       </c>
       <c r="I2" t="n">
-        <v>6.694027188471825</v>
+        <v>4.363484845854285</v>
       </c>
       <c r="J2" t="n">
-        <v>147</v>
+        <v>159.8</v>
       </c>
       <c r="K2" t="n">
-        <v>6.148170459575759</v>
+        <v>3.249615361854384</v>
       </c>
       <c r="L2" t="n">
-        <v>148.4</v>
+        <v>160.3</v>
       </c>
       <c r="M2" t="n">
-        <v>10.28785691968935</v>
+        <v>5.21632054229799</v>
       </c>
       <c r="N2" t="n">
-        <v>147.1</v>
+        <v>160</v>
       </c>
       <c r="O2" t="n">
-        <v>13.53846372377605</v>
+        <v>3.286335345030997</v>
       </c>
       <c r="P2" t="n">
-        <v>141.4</v>
+        <v>158.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.210863151735563</v>
+        <v>3.822302970723278</v>
       </c>
       <c r="R2" t="n">
-        <v>142.1</v>
+        <v>159.5</v>
       </c>
       <c r="S2" t="n">
-        <v>11.28228700219951</v>
+        <v>6.216912416947821</v>
       </c>
       <c r="T2" t="n">
-        <v>144.5</v>
+        <v>161.4</v>
       </c>
       <c r="U2" t="n">
-        <v>9.962429422585638</v>
+        <v>6.296030495478877</v>
       </c>
       <c r="V2" t="n">
-        <v>135.7</v>
+        <v>163.5</v>
       </c>
       <c r="W2" t="n">
-        <v>6.634003316248795</v>
+        <v>4.455333881989093</v>
       </c>
       <c r="X2" t="n">
-        <v>145.8</v>
+        <v>163.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.908422980528034</v>
+        <v>4.172529209005012</v>
       </c>
       <c r="Z2" t="n">
-        <v>145.2</v>
+        <v>159</v>
       </c>
       <c r="AA2" t="n">
-        <v>13.22724461102916</v>
+        <v>4.959838707054898</v>
       </c>
       <c r="AB2" t="n">
-        <v>148.4</v>
+        <v>165.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.42988567398342</v>
+        <v>3.32264954516723</v>
       </c>
       <c r="AD2" t="n">
-        <v>139.6</v>
+        <v>169.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>9.090654541890808</v>
+        <v>4.410215414239989</v>
       </c>
       <c r="AF2" t="n">
-        <v>136</v>
+        <v>172.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>5.932958789676531</v>
+        <v>5.814636704042653</v>
       </c>
       <c r="AH2" t="n">
-        <v>142.5</v>
+        <v>178.6</v>
       </c>
       <c r="AI2" t="n">
-        <v>14.69863939281456</v>
+        <v>5.517245689653489</v>
       </c>
       <c r="AJ2" t="n">
-        <v>144.6</v>
+        <v>176.7</v>
       </c>
       <c r="AK2" t="n">
-        <v>24.11721376942204</v>
+        <v>3.63455636907725</v>
       </c>
       <c r="AL2" t="n">
-        <v>140</v>
+        <v>185.7</v>
       </c>
       <c r="AM2" t="n">
-        <v>6.44980619863884</v>
+        <v>9.143850392476903</v>
       </c>
       <c r="AN2" t="n">
-        <v>141.4</v>
+        <v>180.9</v>
       </c>
       <c r="AO2" t="n">
-        <v>17.47684181996278</v>
+        <v>7.751773990513398</v>
       </c>
       <c r="AP2" t="n">
-        <v>139.9</v>
+        <v>178.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>20.83962571640863</v>
+        <v>37.01472679893774</v>
       </c>
       <c r="AR2" t="n">
-        <v>143.8</v>
+        <v>1472.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>18.74459922217597</v>
+        <v>3926.41311631876</v>
       </c>
       <c r="AT2" t="n">
-        <v>154.1</v>
+        <v>210.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>31.11093055503162</v>
+        <v>143.4209189762776</v>
       </c>
       <c r="AV2" t="n">
-        <v>131.8</v>
+        <v>114.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.207313811473277</v>
+        <v>39.74179160531141</v>
       </c>
       <c r="AX2" t="n">
-        <v>147.6</v>
+        <v>113.3</v>
       </c>
       <c r="AY2" t="n">
-        <v>23.39316139387748</v>
+        <v>27.15161137022994</v>
       </c>
       <c r="AZ2" t="n">
-        <v>143.9</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="BA2" t="n">
-        <v>20.67099417057632</v>
+        <v>21.7046078057172</v>
       </c>
       <c r="BB2" t="n">
-        <v>158.6</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>36.17789380270775</v>
+        <v>17.93014221917941</v>
       </c>
       <c r="BD2" t="n">
-        <v>131.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.724196624914574</v>
+        <v>19.85044080115099</v>
       </c>
       <c r="BF2" t="n">
-        <v>149.6</v>
+        <v>86</v>
       </c>
       <c r="BG2" t="n">
-        <v>26.89312179721797</v>
+        <v>18.38477631085023</v>
       </c>
       <c r="BH2" t="n">
-        <v>130.7</v>
+        <v>81</v>
       </c>
       <c r="BI2" t="n">
-        <v>9.327915093953205</v>
+        <v>4</v>
       </c>
       <c r="BJ2" t="n">
-        <v>4291.1</v>
+        <v>5851.299999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>143.0366666666667</v>
+        <v>195.0433333333333</v>
       </c>
     </row>
     <row r="3">
@@ -941,190 +941,190 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>136.1</v>
+        <v>162</v>
       </c>
       <c r="C3" t="n">
-        <v>7.217340230306453</v>
+        <v>5.513619500836088</v>
       </c>
       <c r="D3" t="n">
-        <v>140.3</v>
+        <v>164.7</v>
       </c>
       <c r="E3" t="n">
-        <v>8.544588931013593</v>
+        <v>6.017474553332153</v>
       </c>
       <c r="F3" t="n">
-        <v>143.2</v>
+        <v>165.4</v>
       </c>
       <c r="G3" t="n">
-        <v>6.241794613730894</v>
+        <v>3.852272056851644</v>
       </c>
       <c r="H3" t="n">
-        <v>139.5</v>
+        <v>161.5</v>
       </c>
       <c r="I3" t="n">
-        <v>5.463515351859094</v>
+        <v>3.07408522978788</v>
       </c>
       <c r="J3" t="n">
-        <v>146.1</v>
+        <v>158.1</v>
       </c>
       <c r="K3" t="n">
-        <v>7.51598296964542</v>
+        <v>2.879236009777594</v>
       </c>
       <c r="L3" t="n">
-        <v>143.9</v>
+        <v>159.2</v>
       </c>
       <c r="M3" t="n">
-        <v>4.90815647672321</v>
+        <v>3.762977544445356</v>
       </c>
       <c r="N3" t="n">
-        <v>143.6</v>
+        <v>158.6</v>
       </c>
       <c r="O3" t="n">
-        <v>11.22675376054895</v>
+        <v>2.939387691339814</v>
       </c>
       <c r="P3" t="n">
-        <v>142.3</v>
+        <v>160</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.82635672791175</v>
+        <v>4.47213595499958</v>
       </c>
       <c r="R3" t="n">
-        <v>143.4</v>
+        <v>160.8</v>
       </c>
       <c r="S3" t="n">
-        <v>8.199999999999999</v>
+        <v>3.487119154832539</v>
       </c>
       <c r="T3" t="n">
-        <v>146.3</v>
+        <v>159.2</v>
       </c>
       <c r="U3" t="n">
-        <v>17.92791120013706</v>
+        <v>4.707440918375927</v>
       </c>
       <c r="V3" t="n">
-        <v>144.3</v>
+        <v>163.9</v>
       </c>
       <c r="W3" t="n">
-        <v>14.39479072442528</v>
+        <v>6.7446274915669</v>
       </c>
       <c r="X3" t="n">
-        <v>138.4</v>
+        <v>158</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.221713506718803</v>
+        <v>5.513619500836088</v>
       </c>
       <c r="Z3" t="n">
-        <v>140.7</v>
+        <v>157.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>13.04645545732633</v>
+        <v>5.6471231613982</v>
       </c>
       <c r="AB3" t="n">
-        <v>138.1</v>
+        <v>166.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.30884609498246</v>
+        <v>4.158124577258358</v>
       </c>
       <c r="AD3" t="n">
-        <v>135.6</v>
+        <v>168.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>15.33101431738944</v>
+        <v>5.063595560468865</v>
       </c>
       <c r="AF3" t="n">
-        <v>133.8</v>
+        <v>173.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>8.423775875461075</v>
+        <v>3.047950130825634</v>
       </c>
       <c r="AH3" t="n">
-        <v>143.4</v>
+        <v>177.8</v>
       </c>
       <c r="AI3" t="n">
-        <v>18.56448221739567</v>
+        <v>7.833262411026455</v>
       </c>
       <c r="AJ3" t="n">
-        <v>138.6</v>
+        <v>180</v>
       </c>
       <c r="AK3" t="n">
-        <v>8.114185110040317</v>
+        <v>8.342661445845684</v>
       </c>
       <c r="AL3" t="n">
-        <v>146.9</v>
+        <v>181.9</v>
       </c>
       <c r="AM3" t="n">
-        <v>29.39880949970594</v>
+        <v>7.063285354564121</v>
       </c>
       <c r="AN3" t="n">
-        <v>137.6</v>
+        <v>198.2</v>
       </c>
       <c r="AO3" t="n">
-        <v>11.43853137426304</v>
+        <v>26.94735608552349</v>
       </c>
       <c r="AP3" t="n">
-        <v>130</v>
+        <v>210.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.57355191030904</v>
+        <v>56.27468347312138</v>
       </c>
       <c r="AR3" t="n">
-        <v>135.9</v>
+        <v>184.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.331666447310692</v>
+        <v>88.88312550760126</v>
       </c>
       <c r="AT3" t="n">
-        <v>147.7</v>
+        <v>131.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>25.01619475459847</v>
+        <v>37.63362857870604</v>
       </c>
       <c r="AV3" t="n">
-        <v>134.8</v>
+        <v>117.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.271461589199408</v>
+        <v>92.04542356901835</v>
       </c>
       <c r="AX3" t="n">
-        <v>137</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="AY3" t="n">
-        <v>26.1457453517776</v>
+        <v>23.55928691620355</v>
       </c>
       <c r="AZ3" t="n">
-        <v>140.2</v>
+        <v>88.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>18.61612204515216</v>
+        <v>19.45276329985023</v>
       </c>
       <c r="BB3" t="n">
-        <v>139.1</v>
+        <v>111.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>18.89682513016406</v>
+        <v>37.0491565356082</v>
       </c>
       <c r="BD3" t="n">
-        <v>132.6</v>
+        <v>86.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.343500610861483</v>
+        <v>21.28872941253188</v>
       </c>
       <c r="BF3" t="n">
-        <v>133.9</v>
+        <v>80.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.915716460273957</v>
+        <v>4.142463035441596</v>
       </c>
       <c r="BH3" t="n">
-        <v>131.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>5.532630477449221</v>
+        <v>7.787168933572714</v>
       </c>
       <c r="BJ3" t="n">
-        <v>4184.6</v>
+        <v>4514.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>139.4866666666667</v>
+        <v>150.4866666666667</v>
       </c>
     </row>
     <row r="4">
@@ -1132,190 +1132,190 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>138.6</v>
+        <v>164.1</v>
       </c>
       <c r="C4" t="n">
-        <v>6.232174580353153</v>
+        <v>5.682429058070149</v>
       </c>
       <c r="D4" t="n">
-        <v>142.4</v>
+        <v>164.2</v>
       </c>
       <c r="E4" t="n">
-        <v>8.935323161475472</v>
+        <v>6.867313885355759</v>
       </c>
       <c r="F4" t="n">
-        <v>140.3</v>
+        <v>162.8</v>
       </c>
       <c r="G4" t="n">
-        <v>4.796873982084582</v>
+        <v>5.81033561853358</v>
       </c>
       <c r="H4" t="n">
-        <v>138.3</v>
+        <v>162.1</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4230987451825</v>
+        <v>8.215229759416351</v>
       </c>
       <c r="J4" t="n">
-        <v>143</v>
+        <v>161.9</v>
       </c>
       <c r="K4" t="n">
-        <v>10.295630140987</v>
+        <v>1.757839583124694</v>
       </c>
       <c r="L4" t="n">
-        <v>142.2</v>
+        <v>161</v>
       </c>
       <c r="M4" t="n">
-        <v>5.015974481593781</v>
+        <v>3.714835124201342</v>
       </c>
       <c r="N4" t="n">
-        <v>147.8</v>
+        <v>158.8</v>
       </c>
       <c r="O4" t="n">
-        <v>8.182909018191515</v>
+        <v>3.969886648255841</v>
       </c>
       <c r="P4" t="n">
-        <v>149.9</v>
+        <v>155.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.22136656151477</v>
+        <v>4.565084884205331</v>
       </c>
       <c r="R4" t="n">
-        <v>150.9</v>
+        <v>160.6</v>
       </c>
       <c r="S4" t="n">
-        <v>18.80132974020721</v>
+        <v>4.386342439892262</v>
       </c>
       <c r="T4" t="n">
-        <v>144.9</v>
+        <v>162.1</v>
       </c>
       <c r="U4" t="n">
-        <v>11.10360301884033</v>
+        <v>6.300000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>140.9</v>
+        <v>162.4</v>
       </c>
       <c r="W4" t="n">
-        <v>8.154140052758475</v>
+        <v>4.758150901348127</v>
       </c>
       <c r="X4" t="n">
-        <v>140.1</v>
+        <v>164.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.69144986731757</v>
+        <v>4.437341546466758</v>
       </c>
       <c r="Z4" t="n">
-        <v>139.1</v>
+        <v>158.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.275868534480233</v>
+        <v>4.153311931459037</v>
       </c>
       <c r="AB4" t="n">
-        <v>138.6</v>
+        <v>164.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.616263691415206</v>
+        <v>6.615134163416491</v>
       </c>
       <c r="AD4" t="n">
-        <v>143.5</v>
+        <v>168.6</v>
       </c>
       <c r="AE4" t="n">
-        <v>17.67625525952825</v>
+        <v>5.31413210223457</v>
       </c>
       <c r="AF4" t="n">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="AG4" t="n">
-        <v>6.526867548832288</v>
+        <v>7.745966692414834</v>
       </c>
       <c r="AH4" t="n">
-        <v>136.6</v>
+        <v>177.8</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.670723564306043</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>135.3</v>
+        <v>185.9</v>
       </c>
       <c r="AK4" t="n">
-        <v>6.986415389883427</v>
+        <v>8.780091115700339</v>
       </c>
       <c r="AL4" t="n">
-        <v>142.4</v>
+        <v>179.9</v>
       </c>
       <c r="AM4" t="n">
-        <v>25.48018838234914</v>
+        <v>6.472248450113763</v>
       </c>
       <c r="AN4" t="n">
-        <v>141.6</v>
+        <v>186.1</v>
       </c>
       <c r="AO4" t="n">
-        <v>13.08587024236447</v>
+        <v>12.0287156421623</v>
       </c>
       <c r="AP4" t="n">
-        <v>137</v>
+        <v>197.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.971370023173351</v>
+        <v>27.65212469232699</v>
       </c>
       <c r="AR4" t="n">
-        <v>149.4</v>
+        <v>179.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>28.94201098749014</v>
+        <v>99.50080401685204</v>
       </c>
       <c r="AT4" t="n">
-        <v>137.2</v>
+        <v>107.7</v>
       </c>
       <c r="AU4" t="n">
-        <v>14.68196172178636</v>
+        <v>37.57938264527505</v>
       </c>
       <c r="AV4" t="n">
-        <v>153.4</v>
+        <v>113.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>28.8277643947636</v>
+        <v>41.3653236419105</v>
       </c>
       <c r="AX4" t="n">
-        <v>133.4</v>
+        <v>142.7</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.089499366462674</v>
+        <v>76.04478943359631</v>
       </c>
       <c r="AZ4" t="n">
-        <v>141.1</v>
+        <v>92.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>19.60841656024269</v>
+        <v>24.42867167899229</v>
       </c>
       <c r="BB4" t="n">
-        <v>140.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="BC4" t="n">
-        <v>28.08932181452589</v>
+        <v>20.91626161626403</v>
       </c>
       <c r="BD4" t="n">
-        <v>134</v>
+        <v>89.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.987490219086343</v>
+        <v>25.89227684078788</v>
       </c>
       <c r="BF4" t="n">
-        <v>136.9</v>
+        <v>78</v>
       </c>
       <c r="BG4" t="n">
-        <v>22.35821996492565</v>
+        <v>3.687817782917155</v>
       </c>
       <c r="BH4" t="n">
-        <v>137.3</v>
+        <v>73.8</v>
       </c>
       <c r="BI4" t="n">
-        <v>13.71167385843173</v>
+        <v>8.352245207128439</v>
       </c>
       <c r="BJ4" t="n">
-        <v>4232.400000000001</v>
+        <v>4497.699999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>141.08</v>
+        <v>149.9233333333333</v>
       </c>
     </row>
     <row r="5">
@@ -1323,190 +1323,190 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>140.2</v>
+        <v>163.4</v>
       </c>
       <c r="C5" t="n">
-        <v>6.43117407632541</v>
+        <v>2.615339366124404</v>
       </c>
       <c r="D5" t="n">
-        <v>140.9</v>
+        <v>162.9</v>
       </c>
       <c r="E5" t="n">
-        <v>6.685057965343308</v>
+        <v>3.360059523282289</v>
       </c>
       <c r="F5" t="n">
-        <v>139.4</v>
+        <v>165.1</v>
       </c>
       <c r="G5" t="n">
-        <v>6.755738301621816</v>
+        <v>3.330165161069342</v>
       </c>
       <c r="H5" t="n">
-        <v>140.7</v>
+        <v>163.7</v>
       </c>
       <c r="I5" t="n">
-        <v>9.000555538409838</v>
+        <v>4.517742799230607</v>
       </c>
       <c r="J5" t="n">
-        <v>140.2</v>
+        <v>160.2</v>
       </c>
       <c r="K5" t="n">
-        <v>7.493997598078078</v>
+        <v>2.925747767665559</v>
       </c>
       <c r="L5" t="n">
-        <v>143.7</v>
+        <v>160.1</v>
       </c>
       <c r="M5" t="n">
-        <v>10.32521186223314</v>
+        <v>3.269556544854363</v>
       </c>
       <c r="N5" t="n">
-        <v>143.5</v>
+        <v>160.8</v>
       </c>
       <c r="O5" t="n">
-        <v>7.697402159170326</v>
+        <v>2.08806130178211</v>
       </c>
       <c r="P5" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.746794344808963</v>
+        <v>4.538722287164087</v>
       </c>
       <c r="R5" t="n">
-        <v>137.8</v>
+        <v>161.9</v>
       </c>
       <c r="S5" t="n">
-        <v>8.047359815492284</v>
+        <v>2.50798724079689</v>
       </c>
       <c r="T5" t="n">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="U5" t="n">
-        <v>12.86079313261822</v>
+        <v>4.219004621945797</v>
       </c>
       <c r="V5" t="n">
-        <v>144.8</v>
+        <v>164.2</v>
       </c>
       <c r="W5" t="n">
-        <v>14.8848916690717</v>
+        <v>6.881860213634101</v>
       </c>
       <c r="X5" t="n">
-        <v>145.8</v>
+        <v>160.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.98427688513067</v>
+        <v>4.715930449020639</v>
       </c>
       <c r="Z5" t="n">
-        <v>139.1</v>
+        <v>157.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.640030120413612</v>
+        <v>4.614108798023731</v>
       </c>
       <c r="AB5" t="n">
-        <v>148.1</v>
+        <v>165.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>15.7</v>
+        <v>6.037383539249433</v>
       </c>
       <c r="AD5" t="n">
-        <v>145.2</v>
+        <v>169.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>18.1758080975785</v>
+        <v>8.077128202523468</v>
       </c>
       <c r="AF5" t="n">
-        <v>147.8</v>
+        <v>171.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>24.55117105149976</v>
+        <v>5.325410782277738</v>
       </c>
       <c r="AH5" t="n">
-        <v>138.9</v>
+        <v>178.1</v>
       </c>
       <c r="AI5" t="n">
-        <v>16.3978657147813</v>
+        <v>6.073713855624086</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150.6</v>
+        <v>180.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>22.81315410021157</v>
+        <v>4.859012245302536</v>
       </c>
       <c r="AL5" t="n">
-        <v>134.7</v>
+        <v>184.3</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.579106033634656</v>
+        <v>5.728001396647874</v>
       </c>
       <c r="AN5" t="n">
-        <v>139</v>
+        <v>190.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>11.61034021895999</v>
+        <v>13.78586232340944</v>
       </c>
       <c r="AP5" t="n">
-        <v>135.4</v>
+        <v>185.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17.26383503164925</v>
+        <v>51.96623904036158</v>
       </c>
       <c r="AR5" t="n">
-        <v>137.2</v>
+        <v>150.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.389355675444401</v>
+        <v>56.12031717658054</v>
       </c>
       <c r="AT5" t="n">
-        <v>138</v>
+        <v>197.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>16.01873902652765</v>
+        <v>139.5386684758028</v>
       </c>
       <c r="AV5" t="n">
-        <v>139.1</v>
+        <v>100.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>22.98020887633531</v>
+        <v>39.5074676485345</v>
       </c>
       <c r="AX5" t="n">
-        <v>144.5</v>
+        <v>128.7</v>
       </c>
       <c r="AY5" t="n">
-        <v>25.62908504024285</v>
+        <v>81.7753630380202</v>
       </c>
       <c r="AZ5" t="n">
-        <v>143.6</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="BA5" t="n">
-        <v>25.02079135439165</v>
+        <v>20.98189695904543</v>
       </c>
       <c r="BB5" t="n">
-        <v>128.8</v>
+        <v>93.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.846018098373212</v>
+        <v>31.71135443338868</v>
       </c>
       <c r="BD5" t="n">
-        <v>138.3</v>
+        <v>86.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>29.09312633595778</v>
+        <v>21.60925727552893</v>
       </c>
       <c r="BF5" t="n">
-        <v>151.1</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="BG5" t="n">
-        <v>40.40408395199673</v>
+        <v>20.93537675801418</v>
       </c>
       <c r="BH5" t="n">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="BI5" t="n">
-        <v>21.60092590608097</v>
+        <v>7.974960814950754</v>
       </c>
       <c r="BJ5" t="n">
-        <v>4249.4</v>
+        <v>4541.600000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>141.6466666666666</v>
+        <v>151.3866666666667</v>
       </c>
     </row>
     <row r="6">
@@ -1514,190 +1514,190 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>139</v>
+        <v>164.2</v>
       </c>
       <c r="C6" t="n">
-        <v>5.656854249492381</v>
+        <v>7.533923280734944</v>
       </c>
       <c r="D6" t="n">
-        <v>141.9</v>
+        <v>162.3</v>
       </c>
       <c r="E6" t="n">
-        <v>6.977822009767805</v>
+        <v>3.976179070414208</v>
       </c>
       <c r="F6" t="n">
-        <v>141.2</v>
+        <v>165.7</v>
       </c>
       <c r="G6" t="n">
-        <v>7.277362159464101</v>
+        <v>4.583666654546335</v>
       </c>
       <c r="H6" t="n">
-        <v>137.1</v>
+        <v>160.7</v>
       </c>
       <c r="I6" t="n">
-        <v>5.337602458033007</v>
+        <v>3.661966684720111</v>
       </c>
       <c r="J6" t="n">
-        <v>148.4</v>
+        <v>162.3</v>
       </c>
       <c r="K6" t="n">
-        <v>9.583318840568751</v>
+        <v>2.647640458974745</v>
       </c>
       <c r="L6" t="n">
-        <v>141.9</v>
+        <v>160.3</v>
       </c>
       <c r="M6" t="n">
-        <v>8.653900854527974</v>
+        <v>2.282542442102665</v>
       </c>
       <c r="N6" t="n">
-        <v>136.6</v>
+        <v>160.9</v>
       </c>
       <c r="O6" t="n">
-        <v>5.834380858325929</v>
+        <v>3.618010503025109</v>
       </c>
       <c r="P6" t="n">
-        <v>154.8</v>
+        <v>159</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.109253973085318</v>
+        <v>4.427188724235731</v>
       </c>
       <c r="R6" t="n">
-        <v>140.4</v>
+        <v>159.9</v>
       </c>
       <c r="S6" t="n">
-        <v>7.748548251124206</v>
+        <v>2.426932219902319</v>
       </c>
       <c r="T6" t="n">
-        <v>146.1</v>
+        <v>160.4</v>
       </c>
       <c r="U6" t="n">
-        <v>9.353608929178085</v>
+        <v>2.8</v>
       </c>
       <c r="V6" t="n">
-        <v>141.1</v>
+        <v>159.9</v>
       </c>
       <c r="W6" t="n">
-        <v>10.29028668210949</v>
+        <v>4.036087214122113</v>
       </c>
       <c r="X6" t="n">
-        <v>144</v>
+        <v>161.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.83666631586332</v>
+        <v>4.983974317750845</v>
       </c>
       <c r="Z6" t="n">
-        <v>143.4</v>
+        <v>159.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>12.31421942308972</v>
+        <v>4.177319714841085</v>
       </c>
       <c r="AB6" t="n">
-        <v>139.3</v>
+        <v>161.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.19430612821347</v>
+        <v>5.71314274283428</v>
       </c>
       <c r="AD6" t="n">
-        <v>141.8</v>
+        <v>167.6</v>
       </c>
       <c r="AE6" t="n">
-        <v>17.54308980767071</v>
+        <v>5.238320341483519</v>
       </c>
       <c r="AF6" t="n">
-        <v>138.2</v>
+        <v>172.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.18031198286809</v>
+        <v>5.146843692983109</v>
       </c>
       <c r="AH6" t="n">
-        <v>133.1</v>
+        <v>175.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>7.555792479945437</v>
+        <v>7.102112361825881</v>
       </c>
       <c r="AJ6" t="n">
-        <v>139.4</v>
+        <v>180.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>13.98713694792469</v>
+        <v>4.270831300812524</v>
       </c>
       <c r="AL6" t="n">
-        <v>137.7</v>
+        <v>183.1</v>
       </c>
       <c r="AM6" t="n">
-        <v>8.718371407550841</v>
+        <v>8.067837380611982</v>
       </c>
       <c r="AN6" t="n">
-        <v>136.9</v>
+        <v>183.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>10.25134137564446</v>
+        <v>13.54437152473307</v>
       </c>
       <c r="AP6" t="n">
-        <v>144</v>
+        <v>185.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>26.81044572550035</v>
+        <v>49.501111098641</v>
       </c>
       <c r="AR6" t="n">
-        <v>135.6</v>
+        <v>207.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>13.03226764611593</v>
+        <v>84.61211497179349</v>
       </c>
       <c r="AT6" t="n">
-        <v>142.5</v>
+        <v>230.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>22.95756955777331</v>
+        <v>310.4764242257373</v>
       </c>
       <c r="AV6" t="n">
-        <v>133.6</v>
+        <v>123.7</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.172168430816444</v>
+        <v>31.97827387461681</v>
       </c>
       <c r="AX6" t="n">
-        <v>139.6</v>
+        <v>99.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>23.3803336160971</v>
+        <v>36.74180180666158</v>
       </c>
       <c r="AZ6" t="n">
-        <v>139.8</v>
+        <v>95.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>20.23758878918138</v>
+        <v>18.9356806056714</v>
       </c>
       <c r="BB6" t="n">
-        <v>138.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="BC6" t="n">
-        <v>23.9459808736247</v>
+        <v>19.95720421301541</v>
       </c>
       <c r="BD6" t="n">
-        <v>133.1</v>
+        <v>85</v>
       </c>
       <c r="BE6" t="n">
-        <v>12.20204900826087</v>
+        <v>17.75387281693772</v>
       </c>
       <c r="BF6" t="n">
-        <v>146.5</v>
+        <v>83.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>29.75987231155403</v>
+        <v>10.13706071797935</v>
       </c>
       <c r="BH6" t="n">
-        <v>135.9</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>9.31074647920348</v>
+        <v>9.436100889668358</v>
       </c>
       <c r="BJ6" t="n">
-        <v>4211.2</v>
+        <v>4592.2</v>
       </c>
       <c r="BK6" t="n">
-        <v>140.3733333333333</v>
+        <v>153.0733333333333</v>
       </c>
     </row>
     <row r="7">
@@ -1705,190 +1705,190 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>139.1</v>
+        <v>166.2</v>
       </c>
       <c r="C7" t="n">
-        <v>9.180958555619341</v>
+        <v>9.568698971124549</v>
       </c>
       <c r="D7" t="n">
-        <v>141.9</v>
+        <v>164.5</v>
       </c>
       <c r="E7" t="n">
-        <v>7.764663547121667</v>
+        <v>5.937171043518958</v>
       </c>
       <c r="F7" t="n">
-        <v>142.7</v>
+        <v>165.5</v>
       </c>
       <c r="G7" t="n">
-        <v>7.267048919609665</v>
+        <v>3.827531841800928</v>
       </c>
       <c r="H7" t="n">
-        <v>140.5</v>
+        <v>162.9</v>
       </c>
       <c r="I7" t="n">
-        <v>5.937171043518958</v>
+        <v>7.555792479945437</v>
       </c>
       <c r="J7" t="n">
-        <v>143.7</v>
+        <v>158.1</v>
       </c>
       <c r="K7" t="n">
-        <v>10.39278595950095</v>
+        <v>4.0853396431631</v>
       </c>
       <c r="L7" t="n">
-        <v>141.9</v>
+        <v>160.8</v>
       </c>
       <c r="M7" t="n">
-        <v>5.717516943569122</v>
+        <v>3.187475490101845</v>
       </c>
       <c r="N7" t="n">
-        <v>144.5</v>
+        <v>160.1</v>
       </c>
       <c r="O7" t="n">
-        <v>10.12175874045613</v>
+        <v>4.825971404805461</v>
       </c>
       <c r="P7" t="n">
-        <v>140.4</v>
+        <v>161.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.971960689854328</v>
+        <v>5.268775948927797</v>
       </c>
       <c r="R7" t="n">
-        <v>148.2</v>
+        <v>162.5</v>
       </c>
       <c r="S7" t="n">
-        <v>14.93184516394407</v>
+        <v>3.66742416417845</v>
       </c>
       <c r="T7" t="n">
-        <v>135.2</v>
+        <v>161.8</v>
       </c>
       <c r="U7" t="n">
-        <v>7.717512552629894</v>
+        <v>6.193545026880809</v>
       </c>
       <c r="V7" t="n">
-        <v>137.2</v>
+        <v>161.2</v>
       </c>
       <c r="W7" t="n">
+        <v>4.399999999999999</v>
+      </c>
+      <c r="X7" t="n">
+        <v>160.7</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.267317658670374</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>160.2</v>
+      </c>
+      <c r="AA7" t="n">
         <v>6.852736679604726</v>
       </c>
-      <c r="X7" t="n">
-        <v>136.9</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>6.80367547726962</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>140.2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>10.66583330077871</v>
-      </c>
       <c r="AB7" t="n">
-        <v>138.9</v>
+        <v>160.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.6571866245677</v>
+        <v>5.127377497317708</v>
       </c>
       <c r="AD7" t="n">
-        <v>141.2</v>
+        <v>168.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>16.53360214835231</v>
+        <v>5.287721626560914</v>
       </c>
       <c r="AF7" t="n">
-        <v>142.2</v>
+        <v>172.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>14.31642413453863</v>
+        <v>4.915282290977803</v>
       </c>
       <c r="AH7" t="n">
-        <v>139.9</v>
+        <v>177.1</v>
       </c>
       <c r="AI7" t="n">
-        <v>21.16813643191105</v>
+        <v>6.670082458260917</v>
       </c>
       <c r="AJ7" t="n">
-        <v>134.3</v>
+        <v>180.7</v>
       </c>
       <c r="AK7" t="n">
-        <v>9.818859404228171</v>
+        <v>6.067124524847006</v>
       </c>
       <c r="AL7" t="n">
-        <v>136.4</v>
+        <v>184.1</v>
       </c>
       <c r="AM7" t="n">
-        <v>6.681317235396026</v>
+        <v>6.331666447310692</v>
       </c>
       <c r="AN7" t="n">
-        <v>140.9</v>
+        <v>177.8</v>
       </c>
       <c r="AO7" t="n">
-        <v>6.847627326307997</v>
+        <v>34.24266344781024</v>
       </c>
       <c r="AP7" t="n">
-        <v>143.8</v>
+        <v>185.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>23.31437324913539</v>
+        <v>34.07110212482126</v>
       </c>
       <c r="AR7" t="n">
-        <v>132.5</v>
+        <v>373.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.232976816898969</v>
+        <v>480.102999365761</v>
       </c>
       <c r="AT7" t="n">
-        <v>143.9</v>
+        <v>130.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>13.90287740002047</v>
+        <v>52.74504716084724</v>
       </c>
       <c r="AV7" t="n">
-        <v>139.2</v>
+        <v>150.7</v>
       </c>
       <c r="AW7" t="n">
-        <v>17.16275036233995</v>
+        <v>99.19178393395292</v>
       </c>
       <c r="AX7" t="n">
-        <v>144.7</v>
+        <v>99.3</v>
       </c>
       <c r="AY7" t="n">
-        <v>31.20913327857728</v>
+        <v>25.26281852842236</v>
       </c>
       <c r="AZ7" t="n">
-        <v>134.9</v>
+        <v>116.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.562302626111375</v>
+        <v>36.23865339661506</v>
       </c>
       <c r="BB7" t="n">
-        <v>146.2</v>
+        <v>92.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>21.86229631122952</v>
+        <v>27.0157361550634</v>
       </c>
       <c r="BD7" t="n">
-        <v>146.1</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>27.340263349134</v>
+        <v>22.8799038459518</v>
       </c>
       <c r="BF7" t="n">
-        <v>150.1</v>
+        <v>83</v>
       </c>
       <c r="BG7" t="n">
-        <v>34.95840385372307</v>
+        <v>18.86266153012348</v>
       </c>
       <c r="BH7" t="n">
-        <v>136.4</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>30.22647845846419</v>
+        <v>4.085339643163099</v>
       </c>
       <c r="BJ7" t="n">
-        <v>4224</v>
+        <v>4721.9</v>
       </c>
       <c r="BK7" t="n">
-        <v>140.8</v>
+        <v>157.3966666666666</v>
       </c>
     </row>
     <row r="8">
@@ -1896,190 +1896,190 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>141.2</v>
+        <v>163.3</v>
       </c>
       <c r="C8" t="n">
-        <v>4.621688003316537</v>
+        <v>6.435060217278468</v>
       </c>
       <c r="D8" t="n">
-        <v>140</v>
+        <v>163.8</v>
       </c>
       <c r="E8" t="n">
-        <v>6.308724118235001</v>
+        <v>3.429285639896449</v>
       </c>
       <c r="F8" t="n">
-        <v>137.7</v>
+        <v>164.4</v>
       </c>
       <c r="G8" t="n">
-        <v>4.754997371187496</v>
+        <v>4.8</v>
       </c>
       <c r="H8" t="n">
-        <v>142.3</v>
+        <v>161.4</v>
       </c>
       <c r="I8" t="n">
-        <v>5.348831648126533</v>
+        <v>5.868560300448484</v>
       </c>
       <c r="J8" t="n">
-        <v>140.5</v>
+        <v>160.3</v>
       </c>
       <c r="K8" t="n">
-        <v>7.419568720619818</v>
+        <v>2.830194339616981</v>
       </c>
       <c r="L8" t="n">
-        <v>143.1</v>
+        <v>161.1</v>
       </c>
       <c r="M8" t="n">
-        <v>7.105631569396206</v>
+        <v>2.256102834535695</v>
       </c>
       <c r="N8" t="n">
-        <v>147.6</v>
+        <v>161.4</v>
       </c>
       <c r="O8" t="n">
-        <v>7.825599018605541</v>
+        <v>2.2</v>
       </c>
       <c r="P8" t="n">
-        <v>143.2</v>
+        <v>160.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.997499609252881</v>
+        <v>4.109744517606903</v>
       </c>
       <c r="R8" t="n">
-        <v>144</v>
+        <v>160.8</v>
       </c>
       <c r="S8" t="n">
-        <v>11.74734012447073</v>
+        <v>2.521904042583698</v>
       </c>
       <c r="T8" t="n">
-        <v>143.7</v>
+        <v>161.2</v>
       </c>
       <c r="U8" t="n">
-        <v>11.18972743189038</v>
+        <v>3.682390527904394</v>
       </c>
       <c r="V8" t="n">
-        <v>152.9</v>
+        <v>162.2</v>
       </c>
       <c r="W8" t="n">
-        <v>13.52368293032634</v>
+        <v>6.63023378170031</v>
       </c>
       <c r="X8" t="n">
-        <v>152.2</v>
+        <v>163.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.84171707865028</v>
+        <v>3.666060555964672</v>
       </c>
       <c r="Z8" t="n">
-        <v>140.2</v>
+        <v>159.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.69444312483497</v>
+        <v>4.050925820105819</v>
       </c>
       <c r="AB8" t="n">
-        <v>143.1</v>
+        <v>163.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>14.8489056835849</v>
+        <v>4.94064773081425</v>
       </c>
       <c r="AD8" t="n">
-        <v>143.1</v>
+        <v>170.8</v>
       </c>
       <c r="AE8" t="n">
-        <v>19.87183937133148</v>
+        <v>4.833218389437828</v>
       </c>
       <c r="AF8" t="n">
-        <v>137.8</v>
+        <v>176.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.77534028617805</v>
+        <v>2.785677655436824</v>
       </c>
       <c r="AH8" t="n">
-        <v>140.3</v>
+        <v>174.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>23.13892823792839</v>
+        <v>5.714017850864661</v>
       </c>
       <c r="AJ8" t="n">
-        <v>140.5</v>
+        <v>179.9</v>
       </c>
       <c r="AK8" t="n">
-        <v>18.96971270209436</v>
+        <v>5.539855593785816</v>
       </c>
       <c r="AL8" t="n">
-        <v>141.9</v>
+        <v>183.6</v>
       </c>
       <c r="AM8" t="n">
-        <v>14.91609868564833</v>
+        <v>7.227724399837061</v>
       </c>
       <c r="AN8" t="n">
-        <v>142.4</v>
+        <v>188.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>19.66824852395352</v>
+        <v>17.79466212098448</v>
       </c>
       <c r="AP8" t="n">
-        <v>145.1</v>
+        <v>206.3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>24.80100804402918</v>
+        <v>105.4400777693188</v>
       </c>
       <c r="AR8" t="n">
-        <v>142.1</v>
+        <v>181.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>23.83044271514904</v>
+        <v>47.39926159762407</v>
       </c>
       <c r="AT8" t="n">
-        <v>143.4</v>
+        <v>135.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>12.47557613900056</v>
+        <v>32.10373810010292</v>
       </c>
       <c r="AV8" t="n">
-        <v>133.1</v>
+        <v>122.7</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.203048213926332</v>
+        <v>38.97961005448875</v>
       </c>
       <c r="AX8" t="n">
-        <v>143.3</v>
+        <v>106.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>23.75731466306745</v>
+        <v>30.31583744513748</v>
       </c>
       <c r="AZ8" t="n">
-        <v>134.2</v>
+        <v>80.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.455272678794342</v>
+        <v>5.481788029466299</v>
       </c>
       <c r="BB8" t="n">
-        <v>130.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>8.868483523128406</v>
+        <v>19.0601678901315</v>
       </c>
       <c r="BD8" t="n">
-        <v>132.1</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>10.63437821407533</v>
+        <v>5.769748694700663</v>
       </c>
       <c r="BF8" t="n">
-        <v>132.2</v>
+        <v>83.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>20.4</v>
+        <v>16.91183017890139</v>
       </c>
       <c r="BH8" t="n">
-        <v>155</v>
+        <v>78.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>34.64101615137755</v>
+        <v>2.959729717389749</v>
       </c>
       <c r="BJ8" t="n">
-        <v>4248.700000000001</v>
+        <v>4506.600000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>141.6233333333334</v>
+        <v>150.2200000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2087,190 +2087,190 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>143.6</v>
+        <v>163.4</v>
       </c>
       <c r="C9" t="n">
-        <v>5.425863986500215</v>
+        <v>5.332916650389354</v>
       </c>
       <c r="D9" t="n">
-        <v>139.1</v>
+        <v>166.4</v>
       </c>
       <c r="E9" t="n">
-        <v>8.814193099768124</v>
+        <v>6.151422599691879</v>
       </c>
       <c r="F9" t="n">
-        <v>140.4</v>
+        <v>162.3</v>
       </c>
       <c r="G9" t="n">
-        <v>6.483826030978931</v>
+        <v>5.367494760127856</v>
       </c>
       <c r="H9" t="n">
-        <v>144.3</v>
+        <v>159.7</v>
       </c>
       <c r="I9" t="n">
-        <v>4.87954915950234</v>
+        <v>6.356886030125128</v>
       </c>
       <c r="J9" t="n">
-        <v>139.3</v>
+        <v>160.6</v>
       </c>
       <c r="K9" t="n">
-        <v>7.043436661176133</v>
+        <v>3.773592452822641</v>
       </c>
       <c r="L9" t="n">
-        <v>144.3</v>
+        <v>161.7</v>
       </c>
       <c r="M9" t="n">
-        <v>7.950471684120383</v>
+        <v>2.968164415931166</v>
       </c>
       <c r="N9" t="n">
-        <v>144.9</v>
+        <v>160.3</v>
       </c>
       <c r="O9" t="n">
-        <v>13.69269878438871</v>
+        <v>3.522782990761707</v>
       </c>
       <c r="P9" t="n">
-        <v>142.9</v>
+        <v>161.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.69065012054926</v>
+        <v>3.773592452822641</v>
       </c>
       <c r="R9" t="n">
-        <v>139.4</v>
+        <v>162.4</v>
       </c>
       <c r="S9" t="n">
-        <v>5.10294032886923</v>
+        <v>2.497999199359359</v>
       </c>
       <c r="T9" t="n">
-        <v>144.3</v>
+        <v>159</v>
       </c>
       <c r="U9" t="n">
-        <v>6.388270501473776</v>
+        <v>4.626013402488151</v>
       </c>
       <c r="V9" t="n">
-        <v>144.6</v>
+        <v>164.6</v>
       </c>
       <c r="W9" t="n">
-        <v>15.76832267554162</v>
+        <v>2.615339366124404</v>
       </c>
       <c r="X9" t="n">
-        <v>137.8</v>
+        <v>157</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.6</v>
+        <v>5.329165037789691</v>
       </c>
       <c r="Z9" t="n">
-        <v>146.2</v>
+        <v>160.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>15.13803157613301</v>
+        <v>3.930648801406709</v>
       </c>
       <c r="AB9" t="n">
-        <v>138</v>
+        <v>165.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.63014581273465</v>
+        <v>6.08687111741328</v>
       </c>
       <c r="AD9" t="n">
-        <v>139.9</v>
+        <v>171.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>8.395832299420945</v>
+        <v>5.107837115648853</v>
       </c>
       <c r="AF9" t="n">
-        <v>137.9</v>
+        <v>173.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>10.86692228738202</v>
+        <v>5.381449618829484</v>
       </c>
       <c r="AH9" t="n">
-        <v>143</v>
+        <v>174.7</v>
       </c>
       <c r="AI9" t="n">
-        <v>15.86820720812531</v>
+        <v>7.294518489934754</v>
       </c>
       <c r="AJ9" t="n">
-        <v>135.8</v>
+        <v>181.8</v>
       </c>
       <c r="AK9" t="n">
-        <v>4.308131845707603</v>
+        <v>5.4</v>
       </c>
       <c r="AL9" t="n">
-        <v>142</v>
+        <v>181.4</v>
       </c>
       <c r="AM9" t="n">
-        <v>22.04087112616014</v>
+        <v>4.882622246293481</v>
       </c>
       <c r="AN9" t="n">
-        <v>145.3</v>
+        <v>187.4</v>
       </c>
       <c r="AO9" t="n">
-        <v>18.64430207865127</v>
+        <v>10.77218640759619</v>
       </c>
       <c r="AP9" t="n">
-        <v>134.5</v>
+        <v>186.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.953990258641679</v>
+        <v>10.81896483033382</v>
       </c>
       <c r="AR9" t="n">
-        <v>143.5</v>
+        <v>201.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>20.2348708916069</v>
+        <v>115.942916989353</v>
       </c>
       <c r="AT9" t="n">
-        <v>135.6</v>
+        <v>110.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>20.48023437365891</v>
+        <v>58.08132229899729</v>
       </c>
       <c r="AV9" t="n">
-        <v>132.2</v>
+        <v>164.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.152621896899067</v>
+        <v>129.0203084789368</v>
       </c>
       <c r="AX9" t="n">
-        <v>156.9</v>
+        <v>103.9</v>
       </c>
       <c r="AY9" t="n">
-        <v>25.7854610197297</v>
+        <v>28.20443227579666</v>
       </c>
       <c r="AZ9" t="n">
-        <v>136.9</v>
+        <v>117.6</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.514105942493316</v>
+        <v>31.8596924027838</v>
       </c>
       <c r="BB9" t="n">
-        <v>135</v>
+        <v>85.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.47213595499958</v>
+        <v>12.47437373177507</v>
       </c>
       <c r="BD9" t="n">
-        <v>128.8</v>
+        <v>86</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.418486873657627</v>
+        <v>21.4289523775662</v>
       </c>
       <c r="BF9" t="n">
-        <v>134.5</v>
+        <v>77.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.5524865872714</v>
+        <v>6.664082832618455</v>
       </c>
       <c r="BH9" t="n">
-        <v>144.1</v>
+        <v>78.3</v>
       </c>
       <c r="BI9" t="n">
-        <v>32.3092865907002</v>
+        <v>4.124318125460256</v>
       </c>
       <c r="BJ9" t="n">
-        <v>4215.000000000001</v>
+        <v>4547.100000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>140.5</v>
+        <v>151.5700000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2278,190 +2278,190 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>141.6</v>
+        <v>164.4</v>
       </c>
       <c r="C10" t="n">
-        <v>5.276362383309167</v>
+        <v>4.223742416388575</v>
       </c>
       <c r="D10" t="n">
-        <v>139.8</v>
+        <v>163.7</v>
       </c>
       <c r="E10" t="n">
-        <v>5.878775382679627</v>
+        <v>6.356886030125128</v>
       </c>
       <c r="F10" t="n">
-        <v>140.2</v>
+        <v>164.1</v>
       </c>
       <c r="G10" t="n">
-        <v>8.646386528486914</v>
+        <v>3.014962686336267</v>
       </c>
       <c r="H10" t="n">
-        <v>140.1</v>
+        <v>162.1</v>
       </c>
       <c r="I10" t="n">
-        <v>5.682429058070149</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>144.3</v>
+        <v>160.3</v>
       </c>
       <c r="K10" t="n">
-        <v>5.692978130996114</v>
+        <v>3.74299345444258</v>
       </c>
       <c r="L10" t="n">
-        <v>143.4</v>
+        <v>162</v>
       </c>
       <c r="M10" t="n">
-        <v>6.770524351924303</v>
+        <v>2.04939015319192</v>
       </c>
       <c r="N10" t="n">
-        <v>142.9</v>
+        <v>160.7</v>
       </c>
       <c r="O10" t="n">
-        <v>5.769748694700663</v>
+        <v>3.226453160980336</v>
       </c>
       <c r="P10" t="n">
-        <v>145.8</v>
+        <v>160.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.19642800182272</v>
+        <v>5.467174773134658</v>
       </c>
       <c r="R10" t="n">
-        <v>145.5</v>
+        <v>160.4</v>
       </c>
       <c r="S10" t="n">
-        <v>10.1316336293808</v>
+        <v>3.136877428271625</v>
       </c>
       <c r="T10" t="n">
-        <v>150.3</v>
+        <v>161.1</v>
       </c>
       <c r="U10" t="n">
-        <v>16.13722404876378</v>
+        <v>4.72122865364515</v>
       </c>
       <c r="V10" t="n">
-        <v>144.5</v>
+        <v>163.3</v>
       </c>
       <c r="W10" t="n">
-        <v>9.510520490488416</v>
+        <v>4.87954915950234</v>
       </c>
       <c r="X10" t="n">
-        <v>142.1</v>
+        <v>160.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.06192356135621</v>
+        <v>4.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>137.4</v>
+        <v>158.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.003332407921454</v>
+        <v>3.436568055487916</v>
       </c>
       <c r="AB10" t="n">
-        <v>140.5</v>
+        <v>162.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.952986860293433</v>
+        <v>4.4328320518603</v>
       </c>
       <c r="AD10" t="n">
-        <v>134.6</v>
+        <v>169.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>13.09350984266633</v>
+        <v>5.161395160225576</v>
       </c>
       <c r="AF10" t="n">
-        <v>149.2</v>
+        <v>175.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.3596116443843</v>
+        <v>5.748043145279966</v>
       </c>
       <c r="AH10" t="n">
-        <v>134.8</v>
+        <v>172.7</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.935585071701226</v>
+        <v>4.648655719667783</v>
       </c>
       <c r="AJ10" t="n">
-        <v>143.2</v>
+        <v>183.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>16.94579593881621</v>
+        <v>6.723838189605696</v>
       </c>
       <c r="AL10" t="n">
-        <v>134.8</v>
+        <v>182.7</v>
       </c>
       <c r="AM10" t="n">
-        <v>5.075431016179808</v>
+        <v>6.812488532100439</v>
       </c>
       <c r="AN10" t="n">
-        <v>134.1</v>
+        <v>180.4</v>
       </c>
       <c r="AO10" t="n">
-        <v>14.55644187293035</v>
+        <v>10.82774214691133</v>
       </c>
       <c r="AP10" t="n">
-        <v>140.1</v>
+        <v>212.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>19.27926347140886</v>
+        <v>104.6066919465481</v>
       </c>
       <c r="AR10" t="n">
-        <v>138.2</v>
+        <v>135.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>21.41868343292836</v>
+        <v>43.4391528462515</v>
       </c>
       <c r="AT10" t="n">
-        <v>138.3</v>
+        <v>142.3</v>
       </c>
       <c r="AU10" t="n">
-        <v>11.80720119249266</v>
+        <v>40.4500927069395</v>
       </c>
       <c r="AV10" t="n">
-        <v>140.1</v>
+        <v>133.7</v>
       </c>
       <c r="AW10" t="n">
-        <v>22.19662136452303</v>
+        <v>96.18528993562373</v>
       </c>
       <c r="AX10" t="n">
-        <v>151.2</v>
+        <v>151.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>25.86812710653788</v>
+        <v>87.7532905365947</v>
       </c>
       <c r="AZ10" t="n">
-        <v>143.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="BA10" t="n">
-        <v>29.1240450487222</v>
+        <v>28.61188564215927</v>
       </c>
       <c r="BB10" t="n">
-        <v>140.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="BC10" t="n">
-        <v>22.0263478588712</v>
+        <v>14.79493156455953</v>
       </c>
       <c r="BD10" t="n">
-        <v>133.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="BE10" t="n">
-        <v>11.42628548566856</v>
+        <v>7.172168430816443</v>
       </c>
       <c r="BF10" t="n">
-        <v>154.5</v>
+        <v>77.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>28.22144574609884</v>
+        <v>8.163945124754331</v>
       </c>
       <c r="BH10" t="n">
-        <v>128.8</v>
+        <v>78.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>6.867313885355759</v>
+        <v>3.827531841800928</v>
       </c>
       <c r="BJ10" t="n">
-        <v>4237.599999999999</v>
+        <v>4521.7</v>
       </c>
       <c r="BK10" t="n">
-        <v>141.2533333333333</v>
+        <v>150.7233333333333</v>
       </c>
     </row>
     <row r="11">
@@ -2469,190 +2469,190 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>141.2</v>
+        <v>164.6</v>
       </c>
       <c r="C11" t="n">
-        <v>7.984985911070851</v>
+        <v>6.15142259969188</v>
       </c>
       <c r="D11" t="n">
-        <v>142.1</v>
+        <v>160.9</v>
       </c>
       <c r="E11" t="n">
-        <v>9.606768447297977</v>
+        <v>5.374941860150676</v>
       </c>
       <c r="F11" t="n">
-        <v>142.3</v>
+        <v>164.4</v>
       </c>
       <c r="G11" t="n">
-        <v>4.920365840057017</v>
+        <v>6.248199740725323</v>
       </c>
       <c r="H11" t="n">
-        <v>142.4</v>
+        <v>160.8</v>
       </c>
       <c r="I11" t="n">
-        <v>4.903060268852505</v>
+        <v>3.310589071449369</v>
       </c>
       <c r="J11" t="n">
-        <v>140.8</v>
+        <v>161.2</v>
       </c>
       <c r="K11" t="n">
-        <v>5.96322060635023</v>
+        <v>2.4</v>
       </c>
       <c r="L11" t="n">
-        <v>138.8</v>
+        <v>159.9</v>
       </c>
       <c r="M11" t="n">
-        <v>6.508456038109192</v>
+        <v>3.590264614203249</v>
       </c>
       <c r="N11" t="n">
-        <v>142.6</v>
+        <v>160.4</v>
       </c>
       <c r="O11" t="n">
-        <v>8.708616422830897</v>
+        <v>3.382306905057553</v>
       </c>
       <c r="P11" t="n">
-        <v>143.7</v>
+        <v>159.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.91833320612629</v>
+        <v>6.220128616033595</v>
       </c>
       <c r="R11" t="n">
-        <v>141.3</v>
+        <v>160.9</v>
       </c>
       <c r="S11" t="n">
-        <v>12.72045596667038</v>
+        <v>5.166236541235795</v>
       </c>
       <c r="T11" t="n">
-        <v>143.8</v>
+        <v>160.3</v>
       </c>
       <c r="U11" t="n">
-        <v>10.29368738596622</v>
+        <v>2.968164415931166</v>
       </c>
       <c r="V11" t="n">
-        <v>140.6</v>
+        <v>164.4</v>
       </c>
       <c r="W11" t="n">
-        <v>17.0598944897089</v>
+        <v>6.545227268781429</v>
       </c>
       <c r="X11" t="n">
-        <v>138.7</v>
+        <v>161.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.957729514719583</v>
+        <v>5.177837386399847</v>
       </c>
       <c r="Z11" t="n">
-        <v>143.7</v>
+        <v>159.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.57626882894484</v>
+        <v>3.112876483254676</v>
       </c>
       <c r="AB11" t="n">
-        <v>139.4</v>
+        <v>163.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.254188241007419</v>
+        <v>6.139218191268331</v>
       </c>
       <c r="AD11" t="n">
-        <v>137.9</v>
+        <v>167.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>9.016096716428899</v>
+        <v>5.044799302251775</v>
       </c>
       <c r="AF11" t="n">
-        <v>139.7</v>
+        <v>175.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>7.810889834071404</v>
+        <v>7.560423268574319</v>
       </c>
       <c r="AH11" t="n">
-        <v>141.1</v>
+        <v>176.9</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.83275357934736</v>
+        <v>5.769748694700663</v>
       </c>
       <c r="AJ11" t="n">
-        <v>139.2</v>
+        <v>179</v>
       </c>
       <c r="AK11" t="n">
-        <v>23.73520591863488</v>
+        <v>4.837354648979129</v>
       </c>
       <c r="AL11" t="n">
-        <v>132.6</v>
+        <v>180.8</v>
       </c>
       <c r="AM11" t="n">
-        <v>4.079215610874227</v>
+        <v>9.184770002564026</v>
       </c>
       <c r="AN11" t="n">
-        <v>145.3</v>
+        <v>197.4</v>
       </c>
       <c r="AO11" t="n">
-        <v>22.01385927092294</v>
+        <v>23.62287027437606</v>
       </c>
       <c r="AP11" t="n">
-        <v>131.5</v>
+        <v>184.7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.5</v>
+        <v>33.096978714076</v>
       </c>
       <c r="AR11" t="n">
-        <v>145.6</v>
+        <v>157.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>23.94660727535323</v>
+        <v>35.51182901513241</v>
       </c>
       <c r="AT11" t="n">
-        <v>140.5</v>
+        <v>139</v>
       </c>
       <c r="AU11" t="n">
-        <v>17.28727855968081</v>
+        <v>55.92852581643825</v>
       </c>
       <c r="AV11" t="n">
-        <v>139.8</v>
+        <v>95</v>
       </c>
       <c r="AW11" t="n">
-        <v>24.55117105149976</v>
+        <v>28.89290570364981</v>
       </c>
       <c r="AX11" t="n">
-        <v>139.8</v>
+        <v>109.1</v>
       </c>
       <c r="AY11" t="n">
-        <v>26.0530228572425</v>
+        <v>30.61192578064961</v>
       </c>
       <c r="AZ11" t="n">
-        <v>143.7</v>
+        <v>109.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>22.77740108089595</v>
+        <v>38.04536765494585</v>
       </c>
       <c r="BB11" t="n">
-        <v>135.4</v>
+        <v>89.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>10.78146557755484</v>
+        <v>17.64539600009022</v>
       </c>
       <c r="BD11" t="n">
-        <v>146</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="BE11" t="n">
-        <v>23.84533497353308</v>
+        <v>19.74056736773287</v>
       </c>
       <c r="BF11" t="n">
-        <v>150.6</v>
+        <v>79.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>28.42604439594085</v>
+        <v>5.714017850864661</v>
       </c>
       <c r="BH11" t="n">
-        <v>145.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>22.43769150336103</v>
+        <v>6.007495318350236</v>
       </c>
       <c r="BJ11" t="n">
-        <v>4235.599999999999</v>
+        <v>4463.1</v>
       </c>
       <c r="BK11" t="n">
-        <v>141.1866666666666</v>
+        <v>148.77</v>
       </c>
     </row>
   </sheetData>
